--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053665</v>
+        <v>120053662</v>
       </c>
       <c r="B18" t="n">
-        <v>108827</v>
+        <v>97813</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,20 +2460,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220320</v>
+        <v>504</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>682847</v>
+        <v>682870</v>
       </c>
       <c r="R18" t="n">
-        <v>6694587</v>
+        <v>6694448</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053662</v>
+        <v>120053667</v>
       </c>
       <c r="B19" t="n">
-        <v>97813</v>
+        <v>97885</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>682870</v>
+        <v>682758</v>
       </c>
       <c r="R19" t="n">
-        <v>6694448</v>
+        <v>6694491</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120053669</v>
+        <v>120053664</v>
       </c>
       <c r="B20" t="n">
-        <v>103418</v>
+        <v>97813</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,16 +2686,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682758</v>
+        <v>682842</v>
       </c>
       <c r="R20" t="n">
-        <v>6694489</v>
+        <v>6694671</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120053664</v>
+        <v>120053668</v>
       </c>
       <c r="B21" t="n">
-        <v>97813</v>
+        <v>101074</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>504</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>682842</v>
+        <v>682758</v>
       </c>
       <c r="R21" t="n">
-        <v>6694671</v>
+        <v>6694489</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120053663</v>
+        <v>120053669</v>
       </c>
       <c r="B22" t="n">
         <v>103418</v>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682870</v>
+        <v>682758</v>
       </c>
       <c r="R22" t="n">
-        <v>6694452</v>
+        <v>6694489</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120053668</v>
+        <v>120053663</v>
       </c>
       <c r="B23" t="n">
-        <v>101074</v>
+        <v>103418</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>682758</v>
+        <v>682870</v>
       </c>
       <c r="R23" t="n">
-        <v>6694489</v>
+        <v>6694452</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053667</v>
+        <v>120053665</v>
       </c>
       <c r="B24" t="n">
-        <v>97885</v>
+        <v>108827</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3126,25 +3126,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>220320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682758</v>
+        <v>682847</v>
       </c>
       <c r="R24" t="n">
-        <v>6694491</v>
+        <v>6694587</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,7 +2448,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053662</v>
+        <v>120053664</v>
       </c>
       <c r="B18" t="n">
         <v>97813</v>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>682870</v>
+        <v>682842</v>
       </c>
       <c r="R18" t="n">
-        <v>6694448</v>
+        <v>6694671</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053667</v>
+        <v>120053669</v>
       </c>
       <c r="B19" t="n">
-        <v>97885</v>
+        <v>103418</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
         <v>682758</v>
       </c>
       <c r="R19" t="n">
-        <v>6694491</v>
+        <v>6694489</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120053664</v>
+        <v>120053663</v>
       </c>
       <c r="B20" t="n">
-        <v>97813</v>
+        <v>103418</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,16 +2686,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>504</v>
+        <v>222412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682842</v>
+        <v>682870</v>
       </c>
       <c r="R20" t="n">
-        <v>6694671</v>
+        <v>6694452</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120053668</v>
+        <v>120053665</v>
       </c>
       <c r="B21" t="n">
-        <v>101074</v>
+        <v>108827</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,25 +2793,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>220320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>682758</v>
+        <v>682847</v>
       </c>
       <c r="R21" t="n">
-        <v>6694489</v>
+        <v>6694587</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120053669</v>
+        <v>120053667</v>
       </c>
       <c r="B22" t="n">
-        <v>103418</v>
+        <v>97885</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2939,7 +2939,7 @@
         <v>682758</v>
       </c>
       <c r="R22" t="n">
-        <v>6694489</v>
+        <v>6694491</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120053663</v>
+        <v>120053666</v>
       </c>
       <c r="B23" t="n">
-        <v>103418</v>
+        <v>108827</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,20 +3015,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>220320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>682870</v>
+        <v>682864</v>
       </c>
       <c r="R23" t="n">
-        <v>6694452</v>
+        <v>6694561</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053665</v>
+        <v>120053662</v>
       </c>
       <c r="B24" t="n">
-        <v>108827</v>
+        <v>97813</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3126,20 +3126,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220320</v>
+        <v>504</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682847</v>
+        <v>682870</v>
       </c>
       <c r="R24" t="n">
-        <v>6694587</v>
+        <v>6694448</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120053666</v>
+        <v>120053668</v>
       </c>
       <c r="B25" t="n">
-        <v>108827</v>
+        <v>101074</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220320</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>682864</v>
+        <v>682758</v>
       </c>
       <c r="R25" t="n">
-        <v>6694561</v>
+        <v>6694489</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -3114,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053662</v>
+        <v>120053668</v>
       </c>
       <c r="B24" t="n">
-        <v>97813</v>
+        <v>101074</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>504</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682870</v>
+        <v>682758</v>
       </c>
       <c r="R24" t="n">
-        <v>6694448</v>
+        <v>6694489</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120053668</v>
+        <v>120053662</v>
       </c>
       <c r="B25" t="n">
-        <v>101074</v>
+        <v>97813</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>504</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>682758</v>
+        <v>682870</v>
       </c>
       <c r="R25" t="n">
-        <v>6694489</v>
+        <v>6694448</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,7 +2448,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053664</v>
+        <v>120053662</v>
       </c>
       <c r="B18" t="n">
         <v>97813</v>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>682842</v>
+        <v>682870</v>
       </c>
       <c r="R18" t="n">
-        <v>6694671</v>
+        <v>6694448</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,7 +2559,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053669</v>
+        <v>120053663</v>
       </c>
       <c r="B19" t="n">
         <v>103418</v>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>682758</v>
+        <v>682870</v>
       </c>
       <c r="R19" t="n">
-        <v>6694489</v>
+        <v>6694452</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120053663</v>
+        <v>120053664</v>
       </c>
       <c r="B20" t="n">
-        <v>103418</v>
+        <v>97813</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,16 +2686,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682870</v>
+        <v>682842</v>
       </c>
       <c r="R20" t="n">
-        <v>6694452</v>
+        <v>6694671</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120053665</v>
+        <v>120053666</v>
       </c>
       <c r="B21" t="n">
         <v>108827</v>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>682847</v>
+        <v>682864</v>
       </c>
       <c r="R21" t="n">
-        <v>6694587</v>
+        <v>6694561</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120053666</v>
+        <v>120053669</v>
       </c>
       <c r="B23" t="n">
-        <v>108827</v>
+        <v>103418</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,20 +3015,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220320</v>
+        <v>222412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>682864</v>
+        <v>682758</v>
       </c>
       <c r="R23" t="n">
-        <v>6694561</v>
+        <v>6694489</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053668</v>
+        <v>120053665</v>
       </c>
       <c r="B24" t="n">
-        <v>101074</v>
+        <v>108827</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3126,25 +3126,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>220320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682758</v>
+        <v>682847</v>
       </c>
       <c r="R24" t="n">
-        <v>6694489</v>
+        <v>6694587</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120053662</v>
+        <v>120053668</v>
       </c>
       <c r="B25" t="n">
-        <v>97813</v>
+        <v>101074</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>504</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>682870</v>
+        <v>682758</v>
       </c>
       <c r="R25" t="n">
-        <v>6694448</v>
+        <v>6694489</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053662</v>
+        <v>120053663</v>
       </c>
       <c r="B18" t="n">
-        <v>97813</v>
+        <v>103418</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>504</v>
+        <v>222412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2495,7 +2495,7 @@
         <v>682870</v>
       </c>
       <c r="R18" t="n">
-        <v>6694448</v>
+        <v>6694452</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053663</v>
+        <v>120053662</v>
       </c>
       <c r="B19" t="n">
-        <v>103418</v>
+        <v>97813</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2606,7 +2606,7 @@
         <v>682870</v>
       </c>
       <c r="R19" t="n">
-        <v>6694452</v>
+        <v>6694448</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053663</v>
+        <v>120053662</v>
       </c>
       <c r="B18" t="n">
-        <v>103418</v>
+        <v>97813</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2495,7 +2495,7 @@
         <v>682870</v>
       </c>
       <c r="R18" t="n">
-        <v>6694452</v>
+        <v>6694448</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053662</v>
+        <v>120053663</v>
       </c>
       <c r="B19" t="n">
-        <v>97813</v>
+        <v>103418</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2606,7 +2606,7 @@
         <v>682870</v>
       </c>
       <c r="R19" t="n">
-        <v>6694448</v>
+        <v>6694452</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053662</v>
+        <v>120053667</v>
       </c>
       <c r="B18" t="n">
-        <v>97813</v>
+        <v>97908</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,21 +2464,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>504</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>682870</v>
+        <v>682758</v>
       </c>
       <c r="R18" t="n">
-        <v>6694448</v>
+        <v>6694491</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053663</v>
+        <v>120053669</v>
       </c>
       <c r="B19" t="n">
-        <v>103418</v>
+        <v>103441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>682870</v>
+        <v>682758</v>
       </c>
       <c r="R19" t="n">
-        <v>6694452</v>
+        <v>6694489</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120053664</v>
+        <v>120053668</v>
       </c>
       <c r="B20" t="n">
-        <v>97813</v>
+        <v>101097</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>504</v>
+        <v>221235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682842</v>
+        <v>682758</v>
       </c>
       <c r="R20" t="n">
-        <v>6694671</v>
+        <v>6694489</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120053666</v>
+        <v>120053665</v>
       </c>
       <c r="B21" t="n">
-        <v>108827</v>
+        <v>108851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>682864</v>
+        <v>682847</v>
       </c>
       <c r="R21" t="n">
-        <v>6694561</v>
+        <v>6694587</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120053667</v>
+        <v>120053664</v>
       </c>
       <c r="B22" t="n">
-        <v>97885</v>
+        <v>97836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682758</v>
+        <v>682842</v>
       </c>
       <c r="R22" t="n">
-        <v>6694491</v>
+        <v>6694671</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120053669</v>
+        <v>120053662</v>
       </c>
       <c r="B23" t="n">
-        <v>103418</v>
+        <v>97836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,16 +3019,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>682758</v>
+        <v>682870</v>
       </c>
       <c r="R23" t="n">
-        <v>6694489</v>
+        <v>6694448</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053665</v>
+        <v>120053666</v>
       </c>
       <c r="B24" t="n">
-        <v>108827</v>
+        <v>108851</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682847</v>
+        <v>682864</v>
       </c>
       <c r="R24" t="n">
-        <v>6694587</v>
+        <v>6694561</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120053668</v>
+        <v>120053663</v>
       </c>
       <c r="B25" t="n">
-        <v>101074</v>
+        <v>103441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>682758</v>
+        <v>682870</v>
       </c>
       <c r="R25" t="n">
-        <v>6694489</v>
+        <v>6694452</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053667</v>
+        <v>120053666</v>
       </c>
       <c r="B18" t="n">
-        <v>97908</v>
+        <v>108851</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,25 +2460,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>220320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>682758</v>
+        <v>682864</v>
       </c>
       <c r="R18" t="n">
-        <v>6694491</v>
+        <v>6694561</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120053668</v>
+        <v>120053663</v>
       </c>
       <c r="B20" t="n">
-        <v>101097</v>
+        <v>103441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682758</v>
+        <v>682870</v>
       </c>
       <c r="R20" t="n">
-        <v>6694489</v>
+        <v>6694452</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120053665</v>
+        <v>120053667</v>
       </c>
       <c r="B21" t="n">
-        <v>108851</v>
+        <v>97908</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,25 +2793,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220320</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>682847</v>
+        <v>682758</v>
       </c>
       <c r="R21" t="n">
-        <v>6694587</v>
+        <v>6694491</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120053664</v>
+        <v>120053665</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
+        <v>108851</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,20 +2904,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>504</v>
+        <v>220320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682842</v>
+        <v>682847</v>
       </c>
       <c r="R22" t="n">
-        <v>6694671</v>
+        <v>6694587</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053666</v>
+        <v>120053668</v>
       </c>
       <c r="B24" t="n">
-        <v>108851</v>
+        <v>101097</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3126,25 +3126,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220320</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682864</v>
+        <v>682758</v>
       </c>
       <c r="R24" t="n">
-        <v>6694561</v>
+        <v>6694489</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120053663</v>
+        <v>120053664</v>
       </c>
       <c r="B25" t="n">
-        <v>103441</v>
+        <v>97836</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3241,16 +3241,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>682870</v>
+        <v>682842</v>
       </c>
       <c r="R25" t="n">
-        <v>6694452</v>
+        <v>6694671</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053666</v>
+        <v>120053668</v>
       </c>
       <c r="B18" t="n">
-        <v>108851</v>
+        <v>101097</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,25 +2460,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220320</v>
+        <v>221235</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>682864</v>
+        <v>682758</v>
       </c>
       <c r="R18" t="n">
-        <v>6694561</v>
+        <v>6694489</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053669</v>
+        <v>120053667</v>
       </c>
       <c r="B19" t="n">
-        <v>103441</v>
+        <v>97908</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
         <v>682758</v>
       </c>
       <c r="R19" t="n">
-        <v>6694489</v>
+        <v>6694491</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120053663</v>
+        <v>120053666</v>
       </c>
       <c r="B20" t="n">
-        <v>103441</v>
+        <v>108851</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222412</v>
+        <v>220320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682870</v>
+        <v>682864</v>
       </c>
       <c r="R20" t="n">
-        <v>6694452</v>
+        <v>6694561</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120053667</v>
+        <v>120053669</v>
       </c>
       <c r="B21" t="n">
-        <v>97908</v>
+        <v>103441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
         <v>682758</v>
       </c>
       <c r="R21" t="n">
-        <v>6694491</v>
+        <v>6694489</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053668</v>
+        <v>120053663</v>
       </c>
       <c r="B24" t="n">
-        <v>101097</v>
+        <v>103441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682758</v>
+        <v>682870</v>
       </c>
       <c r="R24" t="n">
-        <v>6694489</v>
+        <v>6694452</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053668</v>
+        <v>120053669</v>
       </c>
       <c r="B18" t="n">
-        <v>101097</v>
+        <v>103441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,21 +2464,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053667</v>
+        <v>120053666</v>
       </c>
       <c r="B19" t="n">
-        <v>97908</v>
+        <v>108851</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,25 +2571,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>220320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>682758</v>
+        <v>682864</v>
       </c>
       <c r="R19" t="n">
-        <v>6694491</v>
+        <v>6694561</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120053666</v>
+        <v>120053667</v>
       </c>
       <c r="B20" t="n">
-        <v>108851</v>
+        <v>97908</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,25 +2682,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220320</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682864</v>
+        <v>682758</v>
       </c>
       <c r="R20" t="n">
-        <v>6694561</v>
+        <v>6694491</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120053669</v>
+        <v>120053662</v>
       </c>
       <c r="B21" t="n">
-        <v>103441</v>
+        <v>97836</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,16 +2797,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>682758</v>
+        <v>682870</v>
       </c>
       <c r="R21" t="n">
-        <v>6694489</v>
+        <v>6694448</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120053665</v>
+        <v>120053663</v>
       </c>
       <c r="B22" t="n">
-        <v>108851</v>
+        <v>103441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,20 +2904,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220320</v>
+        <v>222412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682847</v>
+        <v>682870</v>
       </c>
       <c r="R22" t="n">
-        <v>6694587</v>
+        <v>6694452</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120053662</v>
+        <v>120053668</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>101097</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>504</v>
+        <v>221235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>682870</v>
+        <v>682758</v>
       </c>
       <c r="R23" t="n">
-        <v>6694448</v>
+        <v>6694489</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053663</v>
+        <v>120053664</v>
       </c>
       <c r="B24" t="n">
-        <v>103441</v>
+        <v>97836</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3130,16 +3130,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682870</v>
+        <v>682842</v>
       </c>
       <c r="R24" t="n">
-        <v>6694452</v>
+        <v>6694671</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120053664</v>
+        <v>120053665</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>108851</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3237,20 +3237,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>504</v>
+        <v>220320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>682842</v>
+        <v>682847</v>
       </c>
       <c r="R25" t="n">
-        <v>6694671</v>
+        <v>6694587</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053669</v>
+        <v>120053666</v>
       </c>
       <c r="B18" t="n">
-        <v>103441</v>
+        <v>108851</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,20 +2460,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>220320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>682758</v>
+        <v>682864</v>
       </c>
       <c r="R18" t="n">
-        <v>6694489</v>
+        <v>6694561</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053666</v>
+        <v>120053669</v>
       </c>
       <c r="B19" t="n">
-        <v>108851</v>
+        <v>103441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,20 +2571,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220320</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>682864</v>
+        <v>682758</v>
       </c>
       <c r="R19" t="n">
-        <v>6694561</v>
+        <v>6694489</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120053667</v>
+        <v>120053668</v>
       </c>
       <c r="B20" t="n">
-        <v>97908</v>
+        <v>101097</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
         <v>682758</v>
       </c>
       <c r="R20" t="n">
-        <v>6694491</v>
+        <v>6694489</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120053662</v>
+        <v>120053663</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>103441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,16 +2797,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>504</v>
+        <v>222412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2828,7 +2828,7 @@
         <v>682870</v>
       </c>
       <c r="R21" t="n">
-        <v>6694448</v>
+        <v>6694452</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120053663</v>
+        <v>120053667</v>
       </c>
       <c r="B22" t="n">
-        <v>103441</v>
+        <v>97908</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682870</v>
+        <v>682758</v>
       </c>
       <c r="R22" t="n">
-        <v>6694452</v>
+        <v>6694491</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120053668</v>
+        <v>120053664</v>
       </c>
       <c r="B23" t="n">
-        <v>101097</v>
+        <v>97836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221235</v>
+        <v>504</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>682758</v>
+        <v>682842</v>
       </c>
       <c r="R23" t="n">
-        <v>6694489</v>
+        <v>6694671</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3114,7 +3114,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053664</v>
+        <v>120053662</v>
       </c>
       <c r="B24" t="n">
         <v>97836</v>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682842</v>
+        <v>682870</v>
       </c>
       <c r="R24" t="n">
-        <v>6694671</v>
+        <v>6694448</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053666</v>
+        <v>120053663</v>
       </c>
       <c r="B18" t="n">
-        <v>108851</v>
+        <v>103441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,20 +2460,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220320</v>
+        <v>222412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>682864</v>
+        <v>682870</v>
       </c>
       <c r="R18" t="n">
-        <v>6694561</v>
+        <v>6694452</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053669</v>
+        <v>120053664</v>
       </c>
       <c r="B19" t="n">
-        <v>103441</v>
+        <v>97836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>682758</v>
+        <v>682842</v>
       </c>
       <c r="R19" t="n">
-        <v>6694489</v>
+        <v>6694671</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120053668</v>
+        <v>120053665</v>
       </c>
       <c r="B20" t="n">
-        <v>101097</v>
+        <v>108851</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,25 +2682,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>220320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682758</v>
+        <v>682847</v>
       </c>
       <c r="R20" t="n">
-        <v>6694489</v>
+        <v>6694587</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120053663</v>
+        <v>120053666</v>
       </c>
       <c r="B21" t="n">
-        <v>103441</v>
+        <v>108851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,20 +2793,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222412</v>
+        <v>220320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>682870</v>
+        <v>682864</v>
       </c>
       <c r="R21" t="n">
-        <v>6694452</v>
+        <v>6694561</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120053667</v>
+        <v>120053662</v>
       </c>
       <c r="B22" t="n">
-        <v>97908</v>
+        <v>97836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682758</v>
+        <v>682870</v>
       </c>
       <c r="R22" t="n">
-        <v>6694491</v>
+        <v>6694448</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120053664</v>
+        <v>120053669</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>103441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,16 +3019,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>504</v>
+        <v>222412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>682842</v>
+        <v>682758</v>
       </c>
       <c r="R23" t="n">
-        <v>6694671</v>
+        <v>6694489</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053662</v>
+        <v>120053668</v>
       </c>
       <c r="B24" t="n">
-        <v>97836</v>
+        <v>101097</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>504</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682870</v>
+        <v>682758</v>
       </c>
       <c r="R24" t="n">
-        <v>6694448</v>
+        <v>6694489</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120053665</v>
+        <v>120053667</v>
       </c>
       <c r="B25" t="n">
-        <v>108851</v>
+        <v>97908</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220320</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>682847</v>
+        <v>682758</v>
       </c>
       <c r="R25" t="n">
-        <v>6694587</v>
+        <v>6694491</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -2448,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053663</v>
+        <v>120053666</v>
       </c>
       <c r="B18" t="n">
-        <v>103441</v>
+        <v>108851</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,20 +2460,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>220320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>682870</v>
+        <v>682864</v>
       </c>
       <c r="R18" t="n">
-        <v>6694452</v>
+        <v>6694561</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053664</v>
+        <v>120053667</v>
       </c>
       <c r="B19" t="n">
-        <v>97836</v>
+        <v>97908</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>682842</v>
+        <v>682758</v>
       </c>
       <c r="R19" t="n">
-        <v>6694671</v>
+        <v>6694491</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120053665</v>
+        <v>120053663</v>
       </c>
       <c r="B20" t="n">
-        <v>108851</v>
+        <v>103441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220320</v>
+        <v>222412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682847</v>
+        <v>682870</v>
       </c>
       <c r="R20" t="n">
-        <v>6694587</v>
+        <v>6694452</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120053666</v>
+        <v>120053664</v>
       </c>
       <c r="B21" t="n">
-        <v>108851</v>
+        <v>97836</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,20 +2793,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220320</v>
+        <v>504</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>682864</v>
+        <v>682842</v>
       </c>
       <c r="R21" t="n">
-        <v>6694561</v>
+        <v>6694671</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120053662</v>
+        <v>120053669</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
+        <v>103441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2908,16 +2908,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>504</v>
+        <v>222412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682870</v>
+        <v>682758</v>
       </c>
       <c r="R22" t="n">
-        <v>6694448</v>
+        <v>6694489</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120053669</v>
+        <v>120053668</v>
       </c>
       <c r="B23" t="n">
-        <v>103441</v>
+        <v>101097</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053668</v>
+        <v>120053662</v>
       </c>
       <c r="B24" t="n">
-        <v>101097</v>
+        <v>97836</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>504</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682758</v>
+        <v>682870</v>
       </c>
       <c r="R24" t="n">
-        <v>6694489</v>
+        <v>6694448</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120053667</v>
+        <v>120053665</v>
       </c>
       <c r="B25" t="n">
-        <v>97908</v>
+        <v>108851</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>220320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>682758</v>
+        <v>682847</v>
       </c>
       <c r="R25" t="n">
-        <v>6694491</v>
+        <v>6694587</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6766642</v>
+        <v>6766641</v>
       </c>
       <c r="B2" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>162</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenfjärden, 450 m NV om dess sydligaste vik, Upl</t>
+          <t>Stenfjärden, 500 m V om dess sydligaste vik, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>682845.8456623721</v>
+        <v>682710</v>
       </c>
       <c r="R2" t="n">
-        <v>6694667.185636681</v>
+        <v>6694360</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +752,14 @@
           <t>2007-06-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-06-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>68 ex (67 blr)</t>
+          <t>162 ex (102 blr)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6773600</v>
+        <v>6766642</v>
       </c>
       <c r="B3" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,14 +830,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenfjärden, 500 m V om dess sydligaste vik, Upl</t>
+          <t>Stenfjärden, 450 m NV om dess sydligaste vik, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682714.5028605335</v>
+        <v>682846</v>
       </c>
       <c r="R3" t="n">
-        <v>6694375.475537388</v>
+        <v>6694667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,27 +864,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-06-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-06-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>40 ex (med 7 klockor)</t>
+          <t>68 ex (67 blr)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6766641</v>
+        <v>6773600</v>
       </c>
       <c r="B4" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682709.7992698627</v>
+        <v>682715</v>
       </c>
       <c r="R4" t="n">
-        <v>6694360.363486546</v>
+        <v>6694375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,27 +979,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-06-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-06-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-06-25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>162 ex (102 blr)</t>
+          <t>40 ex (med 7 klockor)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,32 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111943988</v>
+        <v>6773601</v>
       </c>
       <c r="B5" t="n">
-        <v>107576</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220320</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1098,17 +1048,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenfjärden SV, Upl</t>
+          <t>Stenfjärden, 300 m V om dess sydligaste vik, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>682930</v>
+        <v>682924</v>
       </c>
       <c r="R5" t="n">
-        <v>6694720</v>
+        <v>6694418</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,12 +1094,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2000-06-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2000-06-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>349 ex (med 178 klockor)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,31 +1119,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Floraväkterisamordn C-län</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+          <t>Floraväkteri C-län</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111943983</v>
+        <v>75541620</v>
       </c>
       <c r="B6" t="n">
-        <v>90826</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,37 +1146,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenfjärden SV, Upl</t>
+          <t>Stenfjärden, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>682871</v>
+        <v>682909</v>
       </c>
       <c r="R6" t="n">
-        <v>6694481</v>
+        <v>6694283</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,12 +1204,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1218,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Maria Jakobsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
+          <t>Maria Jakobsson, Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111943999</v>
+        <v>75541805</v>
       </c>
       <c r="B7" t="n">
-        <v>99874</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,37 +1248,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenfjärden SV, Upl</t>
+          <t>Stenfjärden, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>682757</v>
+        <v>682945</v>
       </c>
       <c r="R7" t="n">
-        <v>6694406</v>
+        <v>6694593</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,12 +1302,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2018-09-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2018-09-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,31 +1322,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Maria Jakobsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
+          <t>Maria Jakobsson, Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111943996</v>
+        <v>111943979</v>
       </c>
       <c r="B8" t="n">
-        <v>90480</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,21 +1345,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>504</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1423,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>682785</v>
+        <v>682879</v>
       </c>
       <c r="R8" t="n">
-        <v>6694547</v>
+        <v>6694406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1489,15 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111943997</v>
+        <v>111943981</v>
       </c>
       <c r="B9" t="n">
-        <v>96713</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,39 +1446,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>504</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stenfjärden SV, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>682781</v>
+        <v>682877</v>
       </c>
       <c r="R9" t="n">
-        <v>6694488</v>
+        <v>6694411</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,15 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111943990</v>
+        <v>120053662</v>
       </c>
       <c r="B10" t="n">
-        <v>102192</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,16 +1547,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1634,19 +1565,23 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenfjärden SV, Upl</t>
+          <t>Stenfjärden, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>682930</v>
+        <v>682870</v>
       </c>
       <c r="R10" t="n">
-        <v>6694720</v>
+        <v>6694448</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,12 +1605,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,18 +1619,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Johan Lilja, Cecilia Ronnås</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1706,15 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111943980</v>
+        <v>120053664</v>
       </c>
       <c r="B11" t="n">
-        <v>89331</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,37 +1653,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3215</v>
+        <v>504</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenfjärden SV, Upl</t>
+          <t>Stenfjärden, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>682877</v>
+        <v>682842</v>
       </c>
       <c r="R11" t="n">
-        <v>6694410</v>
+        <v>6694671</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,12 +1711,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,18 +1725,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Johan Lilja, Cecilia Ronnås</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1812,37 +1748,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111943995</v>
+        <v>111943980</v>
       </c>
       <c r="B12" t="n">
-        <v>89047</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3286</v>
+        <v>3215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1852,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>682779</v>
+        <v>682877</v>
       </c>
       <c r="R12" t="n">
-        <v>6694551</v>
+        <v>6694411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,15 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111943984</v>
+        <v>111943992</v>
       </c>
       <c r="B13" t="n">
-        <v>99874</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,21 +1860,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>682929</v>
+        <v>682867</v>
       </c>
       <c r="R13" t="n">
-        <v>6694685</v>
+        <v>6694644</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,15 +1950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111943981</v>
+        <v>111957093</v>
       </c>
       <c r="B14" t="n">
-        <v>96640</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,21 +1961,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>504</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>682877</v>
+        <v>682884</v>
       </c>
       <c r="R14" t="n">
-        <v>6694410</v>
+        <v>6694208</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,37 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111943979</v>
+        <v>111943995</v>
       </c>
       <c r="B15" t="n">
-        <v>96640</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>504</v>
+        <v>3286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>682879</v>
+        <v>682779</v>
       </c>
       <c r="R15" t="n">
-        <v>6694407</v>
+        <v>6694551</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,37 +2152,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111943998</v>
+        <v>111943983</v>
       </c>
       <c r="B16" t="n">
-        <v>98980</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2276,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>682757</v>
+        <v>682871</v>
       </c>
       <c r="R16" t="n">
-        <v>6694406</v>
+        <v>6694480</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,15 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111943992</v>
+        <v>111943996</v>
       </c>
       <c r="B17" t="n">
-        <v>89331</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,21 +2264,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2382,10 +2288,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>682867</v>
+        <v>682785</v>
       </c>
       <c r="R17" t="n">
-        <v>6694644</v>
+        <v>6694547</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,15 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120053664</v>
+        <v>111943997</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2464,41 +2365,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>504</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenfjärden, Upl</t>
+          <t>Stenfjärden SV, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>682842</v>
+        <v>682781</v>
       </c>
       <c r="R18" t="n">
-        <v>6694671</v>
+        <v>6694488</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,12 +2424,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,19 +2438,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Lilja, Cecilia Ronnås</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2559,37 +2460,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120053666</v>
+        <v>120053667</v>
       </c>
       <c r="B19" t="n">
-        <v>108851</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220320</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2603,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>682864</v>
+        <v>682758</v>
       </c>
       <c r="R19" t="n">
-        <v>6694561</v>
+        <v>6694491</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,32 +2566,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120053662</v>
+        <v>111943988</v>
       </c>
       <c r="B20" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>504</v>
+        <v>220320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2704,23 +2595,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenfjärden, Upl</t>
+          <t>Stenfjärden SV, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682870</v>
+        <v>682930</v>
       </c>
       <c r="R20" t="n">
-        <v>6694448</v>
+        <v>6694720</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2744,12 +2631,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2758,19 +2645,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Lilja, Cecilia Ronnås</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2781,37 +2667,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120053668</v>
+        <v>120053665</v>
       </c>
       <c r="B21" t="n">
-        <v>101097</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>220320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2706,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>682758</v>
+        <v>682847</v>
       </c>
       <c r="R21" t="n">
-        <v>6694489</v>
+        <v>6694587</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2892,15 +2773,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120053665</v>
+        <v>120053666</v>
       </c>
       <c r="B22" t="n">
-        <v>108851</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,10 +2812,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682847</v>
+        <v>682864</v>
       </c>
       <c r="R22" t="n">
-        <v>6694587</v>
+        <v>6694561</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3003,57 +2879,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120053667</v>
+        <v>111943984</v>
       </c>
       <c r="B23" t="n">
-        <v>97908</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stenfjärden, Upl</t>
+          <t>Stenfjärden SV, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>682758</v>
+        <v>682930</v>
       </c>
       <c r="R23" t="n">
-        <v>6694491</v>
+        <v>6694685</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3077,12 +2944,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3091,19 +2958,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Lilja, Cecilia Ronnås</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3114,57 +2980,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120053669</v>
+        <v>111943999</v>
       </c>
       <c r="B24" t="n">
-        <v>103441</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stenfjärden, Upl</t>
+          <t>Stenfjärden SV, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>682758</v>
+        <v>682757</v>
       </c>
       <c r="R24" t="n">
-        <v>6694489</v>
+        <v>6694406</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3188,12 +3045,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3202,19 +3059,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Lilja, Cecilia Ronnås</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3225,37 +3081,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120053663</v>
+        <v>120053668</v>
       </c>
       <c r="B25" t="n">
-        <v>103441</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3269,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>682870</v>
+        <v>682758</v>
       </c>
       <c r="R25" t="n">
-        <v>6694452</v>
+        <v>6694489</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3329,6 +3180,420 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>111943990</v>
+      </c>
+      <c r="B26" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stenfjärden SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>682930</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6694720</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120053663</v>
+      </c>
+      <c r="B27" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stenfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>682870</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6694452</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Johan Lilja, Cecilia Ronnås</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120053669</v>
+      </c>
+      <c r="B28" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stenfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>682758</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6694489</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johan Lilja, Cecilia Ronnås</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>111943998</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stenfjärden SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>682757</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6694406</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>

--- a/artfynd/A 45111-2021 artfynd.xlsx
+++ b/artfynd/A 45111-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Floraväkteri C-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6766641</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Floraväkteri C-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6766642</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Floraväkteri C-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6773600</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Floraväkteri C-län</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6773601</t>
         </is>
       </c>
     </row>
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75541620</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75541805</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943979</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1531,6 +1571,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943981</t>
         </is>
       </c>
     </row>
@@ -1639,6 +1684,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120053662</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,6 +1795,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120053664</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,6 +1901,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943980</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1947,6 +2007,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943992</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2048,6 +2113,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111957093</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2149,6 +2219,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943995</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2250,6 +2325,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943983</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2351,6 +2431,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943996</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2455,6 +2540,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943997</t>
         </is>
       </c>
     </row>
@@ -2563,6 +2653,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120053667</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2662,6 +2757,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943988</t>
         </is>
       </c>
     </row>
@@ -2770,6 +2870,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120053665</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2876,6 +2981,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120053666</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2977,6 +3087,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943984</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3076,6 +3191,11 @@
       <c r="AY24" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943999</t>
         </is>
       </c>
     </row>
@@ -3184,6 +3304,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120053668</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3283,6 +3408,11 @@
       <c r="AY26" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943990</t>
         </is>
       </c>
     </row>
@@ -3391,6 +3521,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120053663</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3497,6 +3632,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120053669</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3598,8 +3738,43 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943998</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>